--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_862_Venezuela.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_862_Venezuela.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R6c197bf81e5a4865"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R76177c9d40484738"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R4639110b1a0440e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R4958a904ab5e4672"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R3d52acd7532d44b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R3abd783ac9654bc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R3c0a618cb5564ac2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R824b9f4620df4f14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rb407552f448e465a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Ra37ad7949cd44b5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R0625af820fab4d63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R186aa20ddbc440c1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ862CommercialTable" displayName="EEZ862CommercialTable" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O10"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ862CommercialTable" displayName="EEZ862CommercialTable" ref="A1:E10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E10"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ862FunctionalTable" displayName="EEZ862FunctionalTable" ref="A1:O22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O22"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ862FunctionalTable" displayName="EEZ862FunctionalTable" ref="A1:E22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E22"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ862ValidationTable" displayName="EEZ862ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ862ValidationTable" displayName="EEZ862ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -10945,7 +10899,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce39b926d6694714"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bf5b446e346435d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10955,20 +10909,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -10976,552 +10920,193 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>318.0571173503</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.1019261057887864</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>126.45211737850623</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>318.0571173503</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>145.3881924324908</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$154,A2,'Species'!$U$2:$U$154))</x:f>
-        <x:v>46241.74938184873</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.1019261057887864</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>126.45211737850623</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>40218.99593624947</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>6022.753445599257</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.149748975711523</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.14974897571152282</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>12716.1017932814</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.3922141212688364</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>246.72554744030464</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>12716.1017932814</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>318.41028991421797</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$154,A3,'Species'!$U$2:$U$154))</x:f>
-        <x:v>4048937.658577437</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.3922141212688364</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>246.72554744030464</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>3137387.1762539926</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>911550.4823234444</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.2905444661796017</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.2905444661796018</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>60.65967197309999</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.5262556637686946</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>335.9353169943441</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>60.65967197309999</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>354.6589182334362</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$154,A4,'Species'!$U$2:$U$154))</x:f>
-        <x:v>21513.49364237473</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.5262556637686946</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>335.9353169943441</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>20377.726133056272</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1135.767509318459</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0557357333150161</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.05573573331501611</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>128835.877792763</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.400905303691771</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>251.71280174469112</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>128835.877792763</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>254.59914892379464</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$154,A5,'Species'!$U$2:$U$154))</x:f>
-        <x:v>32801504.836887475</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.400905303691771</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>251.71280174469112</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>32429639.764453005</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>371865.07243447006</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0114668271104905</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.011466827110490487</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>34210.830849656595</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.002666901323948</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>10.061596603971566</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>34210.830849656595</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>10.250800208868842</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$154,A6,'Species'!$U$2:$U$154))</x:f>
-        <x:v>350688.39201923646</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.002666901323948</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>10.061596603971566</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>344215.5794959505</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>6472.812523285975</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.018804530965055</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.018804530965055067</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>27268.778063314105</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.4838884145341615</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>304.71119792323793</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>27268.778063314105</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>466.8022826547736</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$154,A7,'Species'!$U$2:$U$154))</x:f>
-        <x:v>12729127.84516144</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.4838884145341615</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>304.71119792323793</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>8309102.029575353</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>4420025.815586087</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.5319498785613033</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.5319498785613033</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>83867.34182738469</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.661126550107169</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>458.27540522618693</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>83867.34182738469</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1133.5989190973987</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$154,A8,'Species'!$U$2:$U$154))</x:f>
-        <x:v>95071928.04309534</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.661126550107169</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>458.27540522618693</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>38434340.061187856</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>56637587.98190748</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>2.473619369858826</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>1.473619369858826</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>11973.741567095998</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.774760575690387</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>595.3338485611741</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>11973.741567095998</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>655.5119468391943</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$154,A9,'Species'!$U$2:$U$154))</x:f>
-        <x:v>7848930.645596483</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.774760575690387</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>595.3338485611741</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>7128373.648816165</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>720556.9967803182</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1010829443403243</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.10108294434032422</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>7129.0495850158</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.437410380622713</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>2737.8546025800215</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>7129.0495850158</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>2757.3968772714593</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$154,A10,'Species'!$U$2:$U$154))</x:f>
-        <x:v>19657619.06363596</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.437410380622713</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>2737.8546025800215</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>19518301.218356702</x:v>
       </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>139317.84527925774</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0071378058838558</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.007137805883855874</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G10">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O10">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8481113246ba4a51"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red93b3f8c8a547ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11531,20 +11116,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -11552,1200 +11127,421 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1571.8711340783998</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.80027021108404</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>631.3500382047009</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1571.8711340783998</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>631.3551192566943</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$154,A2,'Species'!$U$2:$U$154))</x:f>
-        <x:v>992408.8873122233</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.80027021108404</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>631.3500382047009</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>992400.9005532643</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>7.986758959013969</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0000080479158722</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.000008047915872064752</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.0507230098</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.67</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>467.73514128719813</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.0507230098</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>467.73514128719813</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$154,A3,'Species'!$U$2:$U$154))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>23.724934155314937</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.67</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>467.73514128719813</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>23.724934155314937</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>7.1383080504</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>7.1383080504</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$154,A4,'Species'!$U$2:$U$154))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>15616.916412595265</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>15616.916412595265</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>11469.3917560544</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.393402149903274</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2474.0139829608247</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>11469.3917560544</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2521.475900924994</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$154,A5,'Species'!$U$2:$U$154))</x:f>
-        <x:v>28919794.911158968</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.393402149903274</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2474.0139829608247</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>28375435.580534194</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>544359.3306247741</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0191841753082447</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.019184175308244768</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>3105</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.045523349436393</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1110.512239379957</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>3105</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1110.7094850210215</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$154,A6,'Species'!$U$2:$U$154))</x:f>
-        <x:v>3448752.9509902718</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.045523349436393</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1110.512239379957</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>3448140.5032747667</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>612.4477155050263</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0001776168096757</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0001776168096756419</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>17812.5192636207</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.361949644347602</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2301.174984900595</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>17812.5192636207</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2537.894671096041</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$154,A7,'Species'!$U$2:$U$154))</x:f>
-        <x:v>45206297.71793854</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.361949644347602</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2301.174984900595</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>40989723.74750392</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>4216573.970434621</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.1028690507017966</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.1028690507017967</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>10525.296987382499</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.7191979825788564</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>523.8391856404292</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>10525.296987382499</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>524.1326637642219</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$154,A8,'Species'!$U$2:$U$154))</x:f>
-        <x:v>5516651.946906329</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.7191979825788564</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>523.8391856404292</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>5513563.002494111</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>3088.944412218407</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0005602446930997</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0005602446930997423</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>8446.865475733899</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.563029489529587</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>365.61961712879594</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>8446.865475733899</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>413.02503678531247</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$154,A9,'Species'!$U$2:$U$154))</x:f>
-        <x:v>3488766.92383558</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.563029489529587</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>365.61961712879594</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>3088339.7211762727</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>400427.20265930705</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1296577575043443</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.12965775750434416</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>1448.4445797135</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.1785128504261095</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1508.3872418513454</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>1448.4445797135</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1610.1953304637138</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$154,A10,'Species'!$U$2:$U$154))</x:f>
-        <x:v>2332278.698690154</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.1785128504261095</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1508.3872418513454</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2184815.324568577</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>147463.374121577</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0674946630332227</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.06749466303322262</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>9325.232506779399</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.594258411524258</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>392.8786343590289</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>9325.232506779399</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>403.4347517455433</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$154,A11,'Species'!$U$2:$U$154))</x:f>
-        <x:v>3762122.861342017</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.594258411524258</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>392.8786343590289</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>3663684.6123439143</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>98438.24899810273</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.026868647117287</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.026868647117286912</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>8464.6568926042</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.980129979016809</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>955.2784463755539</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>8464.6568926042</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1054.2126152733008</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$154,A12,'Species'!$U$2:$U$154))</x:f>
-        <x:v>8923548.080143446</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.980129979016809</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>955.2784463755539</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>8086104.2854690645</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>837443.7946743816</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1035657920191915</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.10356579201919143</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>46113.0635230513</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.109052499789877</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>128.54420415131693</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>46113.0635230513</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>358.6450908484499</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$154,A13,'Species'!$U$2:$U$154))</x:f>
-        <x:v>16538223.856525075</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.109052499789877</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>128.54420415131693</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>5927567.051549752</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>10610656.804975323</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>2.7900525987641394</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>1.7900525987641398</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>10740.9073019997</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.4660365357776404</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>292.4398387589098</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>10740.9073019997</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>346.8851616363856</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$154,A14,'Species'!$U$2:$U$154))</x:f>
-        <x:v>3725861.3655756</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.4660365357776404</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>292.4398387589098</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>3141069.199521189</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>584792.1660544109</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.1861761486004683</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.18617614860046827</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>6908.3007773874</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>4.246329309235674</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>1763.3125935015535</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>6908.3007773874</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>2015.751960735962</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$154,A15,'Species'!$U$2:$U$154))</x:f>
-        <x:v>13925420.837372422</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>4.246329309235674</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>1763.3125935015535</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>12181493.760463774</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>1743927.076908648</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.1431620055143592</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.1431620055143593</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>34210.830849656595</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.002666901323948</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>10.061596603971566</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>34210.830849656595</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>10.250800208868842</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$154,A16,'Species'!$U$2:$U$154))</x:f>
-        <x:v>350688.39201923646</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.002666901323948</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>10.061596603971566</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>344215.5794959505</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>6472.812523285975</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.018804530965055</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.018804530965055067</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>3390.869286502</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.8365719469157598</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>68.63915792961599</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>3390.869286502</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>84.58444516783385</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$154,A17,'Species'!$U$2:$U$154))</x:f>
-        <x:v>286814.79723542026</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.8365719469157598</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>68.63915792961599</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>232746.41247489504</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>54068.38476052522</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.232305985667372</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.232305985667372</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>580.6992754108</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.0301527301427025</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>107.18961971459969</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>580.6992754108</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>107.2321054233981</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$154,A18,'Species'!$U$2:$U$154))</x:f>
-        <x:v>62269.605920141796</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.0301527301427025</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>107.18961971459969</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>62244.93449982725</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>24.671420314545685</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0003963602904042</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.0003963602904042602</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>105</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.6100000000000003</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>407.380277804113</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>407.3802778041126</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$154,A19,'Species'!$U$2:$U$154))</x:f>
-        <x:v>42774.92916943182</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.6100000000000003</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>407.380277804113</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>42774.92916943187</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>-4.3655745685100555e-11</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>0.999999999999999</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>-1.020591887181853e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>129153.93491011331</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.400169031414051</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>251.28642711336033</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>129153.93491011331</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>254.33020379232133</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$154,A20,'Species'!$U$2:$U$154))</x:f>
-        <x:v>32847746.586269323</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.400169031414051</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>251.28642711336033</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>32454630.851193875</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>393115.7350754477</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0121127778922492</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.012112777892249129</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>2939.7050447136</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.8014293275506943</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>633.0373395876503</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>2939.7050447136</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>737.7999532656127</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$154,A21,'Species'!$U$2:$U$154))</x:f>
-        <x:v>2168914.24460438</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.8014293275506943</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>633.0373395876503</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>1860943.0606778918</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>307971.18392648804</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.1654919972749205</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.1654919972749206</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>60.65967197309999</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.5262556637686946</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>335.9353169943441</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>60.65967197309999</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>354.6589182334362</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$154,A22,'Species'!$U$2:$U$154))</x:f>
-        <x:v>21513.49364237473</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.5262556637686946</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>335.9353169943441</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>20377.726133056272</x:v>
       </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>1135.767509318459</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1.0557357333150161</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0.05573573331501611</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G22">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O22">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02f0d0b163fd4668"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e69b54eaaf34e56"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12920,7 +11716,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -13019,7 +11815,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>172576491.72799766</x:v>
+        <x:v>109361956.20020832</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13033,7 +11829,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>172576491.72799766</x:v>
+        <x:v>152625911.82444447</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13047,7 +11843,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-63214535.52778934</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13061,7 +11857,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-19950579.903553188</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13072,9 +11868,9 @@
         <x:v>EEZ_862</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -13086,47 +11882,19 @@
         <x:v>EEZ_862</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_862</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_862</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a8f859a69e14f50"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4138416abb84294"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13173,7 +11941,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
